--- a/KatalonData/RADTestData/SSNZeroError.xlsx
+++ b/KatalonData/RADTestData/SSNZeroError.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="25">
   <si>
     <t>Result</t>
   </si>
@@ -96,6 +96,21 @@
   </si>
   <si>
     <t>Fri Oct 02 19:16:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:24:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:24:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:25:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:25:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:25:24 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -502,7 +517,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -519,7 +534,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -536,7 +551,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -553,7 +568,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -580,8 +595,8 @@
       <c r="A7" t="s" s="1">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
+      <c r="B7" t="s" s="1">
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
